--- a/reports/demo_churn/churn_demo_cleaning_report.xlsx
+++ b/reports/demo_churn/churn_demo_cleaning_report.xlsx
@@ -505,7 +505,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1b50cdbe2d21</t>
+          <t>ad22acef44ad</t>
         </is>
       </c>
     </row>
@@ -517,7 +517,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-18T06:33:14+00:00</t>
+          <t>2026-10-18T09:13:49+00:00</t>
         </is>
       </c>
     </row>
@@ -529,7 +529,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-18T06:33:14+00:00</t>
+          <t>2026-10-18T09:13:50+00:00</t>
         </is>
       </c>
     </row>
@@ -553,7 +553,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>374fc97c15434cc5fa6c839301ff3fa6fe20214d9872ed43e8ea7a8f75b6ff85</t>
+          <t>5482fbacf973fd6b26ad9052be23847235d6561a94522317e61389e5856167ee</t>
         </is>
       </c>
     </row>
@@ -565,7 +565,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>fc85c64a8cf816212510fea09933fd37a0e5526651fa3122c037448bb273e168</t>
+          <t>1a0e14293532c464ee36fdfe08c65759354046567efe27c6f2cce39063dab2c3</t>
         </is>
       </c>
     </row>
@@ -589,7 +589,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>a3f52697b5eed944a4c5be7c00e1d2221ac9aad2668cae38cc0a75fb2821a775</t>
+          <t>b41c5a856572fbd1898ef12b8d1b5e3546797bc0df3137eb18bf414dbb95d8a5</t>
         </is>
       </c>
     </row>
@@ -1033,7 +1033,7 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>No target label: this row cannot be used for supervised training.</t>
+          <t>No usable target label: this row cannot be used for supervised training.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1074,7 +1074,7 @@
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>No target label: this row cannot be used for supervised training.</t>
+          <t>No usable target label: this row cannot be used for supervised training.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1386,13 +1386,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="58" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -1441,7 +1441,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>role=identifier</t>
+          <t>role=identifier, status=ready</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>role=datetime</t>
+          <t>role=datetime, status=ready</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1495,7 +1495,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>role=categorical</t>
+          <t>role=categorical, status=ready</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1522,7 +1522,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>role=categorical</t>
+          <t>role=categorical, status=ready</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>role=numeric</t>
+          <t>role=numeric, status=ready</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>role=numeric</t>
+          <t>role=numeric, status=ready</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1603,7 +1603,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>role=numeric</t>
+          <t>role=numeric, status=ready</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>role=pii</t>
+          <t>role=pii, status=ready</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1657,7 +1657,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>role=datetime</t>
+          <t>role=datetime, status=review</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>role=target</t>
+          <t>role=target, status=ready</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1696,7 +1696,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>feature list</t>
+          <t>feature list (ready)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1721,7 +1721,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>feature list</t>
+          <t>feature list (ready)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1746,7 +1746,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>feature list</t>
+          <t>feature list (ready)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1761,17 +1761,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>signup_date, cancellation_date</t>
+          <t>signup_date</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>excluded from features</t>
+          <t>needs review before use</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1781,15 +1781,19 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>identifier</t>
+          <t>cancellation_date</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>customer_id</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
+          <t>possible target leakage: empty -&gt; churn = 'No', filled -&gt; 'Yes' for 99.8% of rows (majority guess: 69.8%)</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>datetime</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1804,12 +1808,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>pii</t>
+          <t>identifier</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>customer_id</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
@@ -1817,7 +1821,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>over 50% missing (kept; decide in your pipeline)</t>
+          <t>excluded from features</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1825,20 +1829,22 @@
           <t>Customers</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>pii</t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>cancellation_date</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>1</v>
-      </c>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>target</t>
+          <t>over 50% missing (kept; decide in your pipeline)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1846,26 +1852,20 @@
           <t>Customers</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>churn</t>
-        </is>
-      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>classification</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2 missing</t>
-        </is>
+          <t>cancellation_date</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>class balance</t>
+          <t>target</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1875,22 +1875,24 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>churn</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>69.8%</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>280</v>
+          <t>classification</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2 missing</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>class balance</t>
+          <t>valid labels</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1900,22 +1902,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>churn</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>30.2%</t>
+          <t>No, Yes</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>121</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>missing labels (rows)</t>
+          <t>class balance</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1923,20 +1925,24 @@
           <t>Customers</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>48, 54</t>
+          <t>69.8%</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2</v>
+        <v>280</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>label conflicts (row groups)</t>
+          <t>class balance</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1944,38 +1950,84 @@
           <t>Customers</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>69 vs 402</t>
+          <t>30.2%</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1</v>
+        <v>121</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>missing labels (rows)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>48, 54</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>label conflicts (row groups)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>69 vs 402</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>possible leakage</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
         <is>
           <t>cancellation_date</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>empty -&gt; churn = 'No', filled -&gt; 'Yes' for 99.8% of rows</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>empty -&gt; churn = 'No', filled -&gt; 'Yes' for 99.8% of rows (majority guess: 69.8%)</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
         <is>
           <t>missingness</t>
         </is>
@@ -3448,7 +3500,7 @@
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>No target label: this row cannot be used for supervised training.</t>
+          <t>No usable target label: this row cannot be used for supervised training.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -3501,7 +3553,7 @@
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>No target label: this row cannot be used for supervised training.</t>
+          <t>No usable target label: this row cannot be used for supervised training.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -3845,7 +3897,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-10-18T06:33:14+00:00</t>
+          <t>2026-10-18T09:13:49+00:00</t>
         </is>
       </c>
     </row>
@@ -3898,7 +3950,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-10-18T06:33:14+00:00</t>
+          <t>2026-10-18T09:13:49+00:00</t>
         </is>
       </c>
     </row>
@@ -3953,7 +4005,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-10-18T06:33:14+00:00</t>
+          <t>2026-10-18T09:13:49+00:00</t>
         </is>
       </c>
     </row>
@@ -4008,7 +4060,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-10-18T06:33:14+00:00</t>
+          <t>2026-10-18T09:13:49+00:00</t>
         </is>
       </c>
     </row>
@@ -4063,7 +4115,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-10-18T06:33:14+00:00</t>
+          <t>2026-10-18T09:13:49+00:00</t>
         </is>
       </c>
     </row>
@@ -4114,7 +4166,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-10-18T06:33:14+00:00</t>
+          <t>2026-10-18T09:13:49+00:00</t>
         </is>
       </c>
     </row>
@@ -4165,7 +4217,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-10-18T06:33:14+00:00</t>
+          <t>2026-10-18T09:13:49+00:00</t>
         </is>
       </c>
     </row>
@@ -4216,7 +4268,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-10-18T06:33:14+00:00</t>
+          <t>2026-10-18T09:13:49+00:00</t>
         </is>
       </c>
     </row>
@@ -4267,7 +4319,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-10-18T06:33:14+00:00</t>
+          <t>2026-10-18T09:13:49+00:00</t>
         </is>
       </c>
     </row>
